--- a/Test/PermisosAsignados.xlsx
+++ b/Test/PermisosAsignados.xlsx
@@ -1,160 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://femcom-my.sharepoint.com/personal/maximiliano_sanpedro_oxxo_com/Documents/Documentos/GitHub/Practica-Oxxo/Test/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_78C8BFFAD26906A6E69944630B83244481028F05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45AFBE4E-50A7-4873-8060-BE2D6CC55632}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Content!$C$1:$C$178</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="771">
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Apellido</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Nombre</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Rut</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Grupo</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Tipo Permiso</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Descripción Permiso</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Fecha Inicio</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Fecha Fin</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Hora inicio</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Hora fin</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Permisos Parciales</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Fijo por horas</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Cantidad Horas</d:t>
-    </d:r>
-  </si>
-  <si>
-    <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-      <d:rPr>
-        <d:b/>
-        <d:sz val="11"/>
-        <d:rFont val="Calibri"/>
-      </d:rPr>
-      <d:t xml:space="preserve">Creado Por</d:t>
-    </d:r>
-  </si>
-  <si>
-    <t xml:space="preserve">LEGUIZAMON	BAREÑO</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="771">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Apellido</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Nombre</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Rut</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Grupo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Tipo Permiso</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Descripción Permiso</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fecha Inicio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fecha Fin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hora inicio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Hora fin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Permisos Parciales</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Fijo por horas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Cantidad Horas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Creado Por</t>
+    </r>
+  </si>
+  <si>
+    <t>LEGUIZAMON	BAREÑO</t>
   </si>
   <si>
     <t>DORA PATRICIA</t>
@@ -292,7 +316,7 @@
     <t>28-04-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">PARADA	CÁCERES</t>
+    <t>PARADA	CÁCERES</t>
   </si>
   <si>
     <t>RUBÉN ALEJANDRO</t>
@@ -442,7 +466,7 @@
     <t>01-04-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">MENDOZA	SALAS</t>
+    <t>MENDOZA	SALAS</t>
   </si>
   <si>
     <t>LIZNEIDY ANDREINA</t>
@@ -487,7 +511,7 @@
     <t>BULNES</t>
   </si>
   <si>
-    <t xml:space="preserve">RIVEROL  ELEJALDE</t>
+    <t>RIVEROL  ELEJALDE</t>
   </si>
   <si>
     <t>DIANA BRIGGIITTE</t>
@@ -550,7 +574,7 @@
     <t>26-04-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">PORTALES 	ROBERTS</t>
+    <t>PORTALES 	ROBERTS</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -607,7 +631,7 @@
     <t>27-06-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">RETAMAL 	PERALTA</t>
+    <t>RETAMAL 	PERALTA</t>
   </si>
   <si>
     <t>MADELINE ALEJANDRA</t>
@@ -619,7 +643,7 @@
     <t>CERRO COLORADO</t>
   </si>
   <si>
-    <t xml:space="preserve">HUENCHUAL	PIÑA</t>
+    <t>HUENCHUAL	PIÑA</t>
   </si>
   <si>
     <t>GABY ESTER</t>
@@ -664,7 +688,7 @@
     <t>20-04-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">REBOLLEDO	GARCIA</t>
+    <t>REBOLLEDO	GARCIA</t>
   </si>
   <si>
     <t>KIMBERLY APRIL</t>
@@ -676,7 +700,7 @@
     <t>20-01-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">ALEGRIA	ORELLANA</t>
+    <t>ALEGRIA	ORELLANA</t>
   </si>
   <si>
     <t>KAREN RAQUEL</t>
@@ -712,7 +736,7 @@
     <t>COSTA MONTEMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">GOMEZ 	ESPINDOLA</t>
+    <t>GOMEZ 	ESPINDOLA</t>
   </si>
   <si>
     <t>ESTEBAN ANDRES</t>
@@ -742,7 +766,7 @@
     <t>Jorge Antonio Moran Molina</t>
   </si>
   <si>
-    <t xml:space="preserve">SAEZ 	ENCINA</t>
+    <t>SAEZ 	ENCINA</t>
   </si>
   <si>
     <t>ESTEBAN ALONSO</t>
@@ -799,7 +823,7 @@
     <t>30-04-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">ORDOÑEZ  RODRIGUEZ</t>
+    <t>ORDOÑEZ  RODRIGUEZ</t>
   </si>
   <si>
     <t>MISAEL DARIO</t>
@@ -823,7 +847,7 @@
     <t>EL RODEO</t>
   </si>
   <si>
-    <t xml:space="preserve">GONZALEZ	SAN MARTIN</t>
+    <t>GONZALEZ	SAN MARTIN</t>
   </si>
   <si>
     <t>NOEMI BELEN</t>
@@ -853,7 +877,7 @@
     <t>16-03-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">REYES	GONZÁLEZ</t>
+    <t>REYES	GONZÁLEZ</t>
   </si>
   <si>
     <t>JAVIERA IGNACIA</t>
@@ -916,7 +940,7 @@
     <t>04-05-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">GUTIERREZ 	RAMOS</t>
+    <t>GUTIERREZ 	RAMOS</t>
   </si>
   <si>
     <t>JEANETH JOSEFINA</t>
@@ -940,7 +964,7 @@
     <t>17-04-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">PALACIOS	IRUYARI</t>
+    <t>PALACIOS	IRUYARI</t>
   </si>
   <si>
     <t>PAOLA</t>
@@ -970,7 +994,7 @@
     <t>22.042.190-2</t>
   </si>
   <si>
-    <t xml:space="preserve">CISTERNAS 	MUÑOZ</t>
+    <t>CISTERNAS 	MUÑOZ</t>
   </si>
   <si>
     <t>SCARLETT CATALINA</t>
@@ -988,7 +1012,7 @@
     <t>05-03-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">ORTEGA	BRITEL</t>
+    <t>ORTEGA	BRITEL</t>
   </si>
   <si>
     <t>JOVANA</t>
@@ -1015,7 +1039,7 @@
     <t>09-03-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">OSPINA	MEJIA</t>
+    <t>OSPINA	MEJIA</t>
   </si>
   <si>
     <t>ANALIDA</t>
@@ -1054,7 +1078,7 @@
     <t>IRARRAZAVAL SAN JORGE</t>
   </si>
   <si>
-    <t xml:space="preserve">GONZALEZ 	ALVAREZ</t>
+    <t>GONZALEZ 	ALVAREZ</t>
   </si>
   <si>
     <t>KATHERIN DE LOS ANGELES</t>
@@ -1081,7 +1105,7 @@
     <t>26.813.021-7</t>
   </si>
   <si>
-    <t xml:space="preserve">JORDAN	VILLAVICENCIO</t>
+    <t>JORDAN	VILLAVICENCIO</t>
   </si>
   <si>
     <t>DARLING FERNANDO</t>
@@ -1186,7 +1210,7 @@
     <t>23-04-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">HARRIS	DEL VALLE</t>
+    <t>HARRIS	DEL VALLE</t>
   </si>
   <si>
     <t>ZLATNA FIORELLA</t>
@@ -1210,7 +1234,7 @@
     <t>LAS BRISAS</t>
   </si>
   <si>
-    <t xml:space="preserve">CASTILLO 	GRUNEWALDT</t>
+    <t>CASTILLO 	GRUNEWALDT</t>
   </si>
   <si>
     <t>ARANTZA FERNANDA</t>
@@ -1234,7 +1258,7 @@
     <t>LAS CONDES 1</t>
   </si>
   <si>
-    <t xml:space="preserve">ARANCIBIA	PONCE</t>
+    <t>ARANCIBIA	PONCE</t>
   </si>
   <si>
     <t>VALENTINA ANTONIA</t>
@@ -1351,7 +1375,7 @@
     <t>LUIS PASTEUR</t>
   </si>
   <si>
-    <t xml:space="preserve">ORELLANA	HERNANDEZ</t>
+    <t>ORELLANA	HERNANDEZ</t>
   </si>
   <si>
     <t>21.267.782-5</t>
@@ -1384,7 +1408,7 @@
     <t>OXXO P. Mudanza</t>
   </si>
   <si>
-    <t xml:space="preserve">CELIN 	FERNANDEZ</t>
+    <t>CELIN 	FERNANDEZ</t>
   </si>
   <si>
     <t>SUSANA</t>
@@ -1444,7 +1468,7 @@
     <t>MALL PASEO VINA</t>
   </si>
   <si>
-    <t xml:space="preserve">CORDERO	SAAVEDRA</t>
+    <t>CORDERO	SAAVEDRA</t>
   </si>
   <si>
     <t>PALOMA IGNACIA BELÉN</t>
@@ -1489,7 +1513,7 @@
     <t>11-02-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">RUIZ TAGLE	ABARCA</t>
+    <t>RUIZ TAGLE	ABARCA</t>
   </si>
   <si>
     <t>JOSEFA ANTUAN</t>
@@ -1501,7 +1525,7 @@
     <t>MANQUEHUE NORTE</t>
   </si>
   <si>
-    <t xml:space="preserve">LAGOS	RAMIREZ</t>
+    <t>LAGOS	RAMIREZ</t>
   </si>
   <si>
     <t>MELISSA ALEJANDRA</t>
@@ -1525,7 +1549,7 @@
     <t>27.210.187-6</t>
   </si>
   <si>
-    <t xml:space="preserve">HERNANDEZ	MENDOZA</t>
+    <t>HERNANDEZ	MENDOZA</t>
   </si>
   <si>
     <t>LUZ MARINA</t>
@@ -1588,7 +1612,7 @@
     <t>14.727.255-3</t>
   </si>
   <si>
-    <t xml:space="preserve">PARRAGUIRRE	ABAYAY</t>
+    <t>PARRAGUIRRE	ABAYAY</t>
   </si>
   <si>
     <t>MARIA FRANCISCA</t>
@@ -1600,7 +1624,7 @@
     <t>METRO GRUTA LOURDES</t>
   </si>
   <si>
-    <t xml:space="preserve">Calderón  Zulueta</t>
+    <t>Calderón  Zulueta</t>
   </si>
   <si>
     <t>Danitza de Jesús</t>
@@ -1663,7 +1687,7 @@
     <t>NATANIEL COX 2</t>
   </si>
   <si>
-    <t xml:space="preserve">ZAMBRANO	LARRIAL</t>
+    <t>ZAMBRANO	LARRIAL</t>
   </si>
   <si>
     <t>NHAIN DEL VALLE</t>
@@ -1675,7 +1699,7 @@
     <t>NORUEGA</t>
   </si>
   <si>
-    <t xml:space="preserve">JIMENEZ	JIMENEZ</t>
+    <t>JIMENEZ	JIMENEZ</t>
   </si>
   <si>
     <t>EVELIN CAROLINA</t>
@@ -1777,7 +1801,7 @@
     <t>PADRE MARIANO</t>
   </si>
   <si>
-    <t xml:space="preserve">CLAROS 	VALDIVIA</t>
+    <t>CLAROS 	VALDIVIA</t>
   </si>
   <si>
     <t>GLORIA</t>
@@ -1801,7 +1825,7 @@
     <t>PATIO BELLAVISTA</t>
   </si>
   <si>
-    <t xml:space="preserve">ORTEGA	MALDONADO</t>
+    <t>ORTEGA	MALDONADO</t>
   </si>
   <si>
     <t>KATHLEEN WENDY</t>
@@ -1981,7 +2005,7 @@
     <t>RECREO I</t>
   </si>
   <si>
-    <t xml:space="preserve">MEDINA	ESPINOZA</t>
+    <t>MEDINA	ESPINOZA</t>
   </si>
   <si>
     <t>BENJAMIN FERNANDO</t>
@@ -2002,7 +2026,7 @@
     <t>RENACA 2</t>
   </si>
   <si>
-    <t xml:space="preserve">FUENTEALBA	CACERES</t>
+    <t>FUENTEALBA	CACERES</t>
   </si>
   <si>
     <t>JOSE ANTONIO</t>
@@ -2077,7 +2101,7 @@
     <t>ROSARIO NORTE 2</t>
   </si>
   <si>
-    <t xml:space="preserve">ARENAS	SANCHEZ</t>
+    <t>ARENAS	SANCHEZ</t>
   </si>
   <si>
     <t>XIMENA LEONTINA CAROLINA</t>
@@ -2113,7 +2137,7 @@
     <t>SAN DAMIAN</t>
   </si>
   <si>
-    <t xml:space="preserve">ARQUEROS	MOLINA</t>
+    <t>ARQUEROS	MOLINA</t>
   </si>
   <si>
     <t>TAMARA JAVIERA</t>
@@ -2173,7 +2197,7 @@
     <t>26.303.731-6</t>
   </si>
   <si>
-    <t xml:space="preserve">CARRASCO 	RIOS</t>
+    <t>CARRASCO 	RIOS</t>
   </si>
   <si>
     <t>MARIA VERONICA</t>
@@ -2185,7 +2209,7 @@
     <t>SEMINARIO</t>
   </si>
   <si>
-    <t xml:space="preserve">HERNANDEZ	LOPEZ</t>
+    <t>HERNANDEZ	LOPEZ</t>
   </si>
   <si>
     <t>FRANCISCA PATRICIA</t>
@@ -2323,7 +2347,7 @@
     <t>VILLUCO</t>
   </si>
   <si>
-    <t xml:space="preserve">Escobar  soto</t>
+    <t>Escobar  soto</t>
   </si>
   <si>
     <t>Andrea marisol</t>
@@ -2356,7 +2380,7 @@
     <t>15-03-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">VIDELA 	AMENGUAL</t>
+    <t>VIDELA 	AMENGUAL</t>
   </si>
   <si>
     <t>SARA ARMONIA</t>
@@ -2428,12 +2452,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[hh]:mm"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -2456,14 +2485,14 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2471,13 +2500,338 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O178"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -2490,13 +2844,12 @@
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="12" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="34" customWidth="1"/>
-    <col min="15" max="15" width="0" customWidth="1"/>
+    <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2541,7 +2894,7 @@
       </c>
       <c r="O1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2581,7 +2934,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -2623,7 +2976,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -2663,7 +3016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>40</v>
       </c>
@@ -2705,7 +3058,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>47</v>
       </c>
@@ -2745,7 +3098,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>54</v>
       </c>
@@ -2785,7 +3138,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>60</v>
       </c>
@@ -2825,7 +3178,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>66</v>
       </c>
@@ -2867,7 +3220,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>72</v>
       </c>
@@ -2907,7 +3260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>77</v>
       </c>
@@ -2947,7 +3300,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>84</v>
       </c>
@@ -2989,7 +3342,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>89</v>
       </c>
@@ -3029,7 +3382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>95</v>
       </c>
@@ -3069,7 +3422,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>101</v>
       </c>
@@ -3109,7 +3462,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>106</v>
       </c>
@@ -3151,7 +3504,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>110</v>
       </c>
@@ -3191,7 +3544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>116</v>
       </c>
@@ -3231,7 +3584,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>121</v>
       </c>
@@ -3273,7 +3626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>125</v>
       </c>
@@ -3313,7 +3666,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>131</v>
       </c>
@@ -3353,7 +3706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>136</v>
       </c>
@@ -3393,7 +3746,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>141</v>
       </c>
@@ -3433,7 +3786,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>146</v>
       </c>
@@ -3475,7 +3828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>151</v>
       </c>
@@ -3515,7 +3868,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>155</v>
       </c>
@@ -3555,7 +3908,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>160</v>
       </c>
@@ -3595,7 +3948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>165</v>
       </c>
@@ -3635,7 +3988,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>169</v>
       </c>
@@ -3677,7 +4030,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>173</v>
       </c>
@@ -3717,7 +4070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>178</v>
       </c>
@@ -3757,7 +4110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>184</v>
       </c>
@@ -3797,7 +4150,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>188</v>
       </c>
@@ -3839,7 +4192,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>192</v>
       </c>
@@ -3879,7 +4232,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>196</v>
       </c>
@@ -3919,7 +4272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>200</v>
       </c>
@@ -3959,7 +4312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>205</v>
       </c>
@@ -3999,7 +4352,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>210</v>
       </c>
@@ -4041,7 +4394,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>213</v>
       </c>
@@ -4081,7 +4434,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>217</v>
       </c>
@@ -4121,7 +4474,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>221</v>
       </c>
@@ -4163,7 +4516,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>225</v>
       </c>
@@ -4203,7 +4556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>229</v>
       </c>
@@ -4243,7 +4596,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>233</v>
       </c>
@@ -4285,7 +4638,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>237</v>
       </c>
@@ -4325,7 +4678,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>242</v>
       </c>
@@ -4365,7 +4718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>247</v>
       </c>
@@ -4407,7 +4760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>250</v>
       </c>
@@ -4449,7 +4802,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>254</v>
       </c>
@@ -4489,7 +4842,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>258</v>
       </c>
@@ -4531,7 +4884,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>262</v>
       </c>
@@ -4571,7 +4924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>268</v>
       </c>
@@ -4613,7 +4966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>271</v>
       </c>
@@ -4653,7 +5006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>276</v>
       </c>
@@ -4695,7 +5048,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>279</v>
       </c>
@@ -4735,7 +5088,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>283</v>
       </c>
@@ -4777,7 +5130,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>286</v>
       </c>
@@ -4817,7 +5170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>292</v>
       </c>
@@ -4857,7 +5210,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>297</v>
       </c>
@@ -4897,7 +5250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>301</v>
       </c>
@@ -4939,7 +5292,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>306</v>
       </c>
@@ -4979,7 +5332,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>310</v>
       </c>
@@ -5019,7 +5372,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>314</v>
       </c>
@@ -5061,7 +5414,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>320</v>
       </c>
@@ -5103,7 +5456,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>323</v>
       </c>
@@ -5143,7 +5496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>326</v>
       </c>
@@ -5185,7 +5538,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>330</v>
       </c>
@@ -5225,7 +5578,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>334</v>
       </c>
@@ -5265,7 +5618,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>338</v>
       </c>
@@ -5305,7 +5658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>341</v>
       </c>
@@ -5347,7 +5700,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>344</v>
       </c>
@@ -5387,7 +5740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>348</v>
       </c>
@@ -5427,7 +5780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>353</v>
       </c>
@@ -5467,7 +5820,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>358</v>
       </c>
@@ -5507,7 +5860,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>362</v>
       </c>
@@ -5547,7 +5900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>366</v>
       </c>
@@ -5587,7 +5940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>370</v>
       </c>
@@ -5627,7 +5980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>374</v>
       </c>
@@ -5667,7 +6020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>378</v>
       </c>
@@ -5707,7 +6060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>383</v>
       </c>
@@ -5749,7 +6102,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>387</v>
       </c>
@@ -5789,7 +6142,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>391</v>
       </c>
@@ -5829,7 +6182,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>396</v>
       </c>
@@ -5869,7 +6222,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>400</v>
       </c>
@@ -5909,7 +6262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>405</v>
       </c>
@@ -5949,7 +6302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>409</v>
       </c>
@@ -5989,7 +6342,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>413</v>
       </c>
@@ -6029,7 +6382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>415</v>
       </c>
@@ -6069,7 +6422,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>419</v>
       </c>
@@ -6109,7 +6462,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>424</v>
       </c>
@@ -6149,7 +6502,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>429</v>
       </c>
@@ -6189,7 +6542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>433</v>
       </c>
@@ -6231,7 +6584,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>436</v>
       </c>
@@ -6271,7 +6624,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>440</v>
       </c>
@@ -6311,7 +6664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>444</v>
       </c>
@@ -6351,7 +6704,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>450</v>
       </c>
@@ -6393,7 +6746,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>454</v>
       </c>
@@ -6433,7 +6786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>459</v>
       </c>
@@ -6473,7 +6826,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>463</v>
       </c>
@@ -6513,7 +6866,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>468</v>
       </c>
@@ -6555,7 +6908,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>471</v>
       </c>
@@ -6595,7 +6948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>475</v>
       </c>
@@ -6637,7 +6990,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>479</v>
       </c>
@@ -6677,7 +7030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>483</v>
       </c>
@@ -6717,7 +7070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>486</v>
       </c>
@@ -6759,7 +7112,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>489</v>
       </c>
@@ -6799,7 +7152,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>492</v>
       </c>
@@ -6839,7 +7192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>496</v>
       </c>
@@ -6879,7 +7232,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>500</v>
       </c>
@@ -6919,7 +7272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>504</v>
       </c>
@@ -6959,7 +7312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>508</v>
       </c>
@@ -6999,7 +7352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>513</v>
       </c>
@@ -7041,7 +7394,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>517</v>
       </c>
@@ -7081,7 +7434,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>521</v>
       </c>
@@ -7121,7 +7474,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>525</v>
       </c>
@@ -7163,7 +7516,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>528</v>
       </c>
@@ -7203,7 +7556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>532</v>
       </c>
@@ -7243,7 +7596,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>536</v>
       </c>
@@ -7283,7 +7636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>539</v>
       </c>
@@ -7323,7 +7676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>544</v>
       </c>
@@ -7365,7 +7718,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>547</v>
       </c>
@@ -7407,7 +7760,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>551</v>
       </c>
@@ -7449,7 +7802,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>555</v>
       </c>
@@ -7489,7 +7842,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>559</v>
       </c>
@@ -7529,7 +7882,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>563</v>
       </c>
@@ -7569,7 +7922,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>567</v>
       </c>
@@ -7609,7 +7962,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>572</v>
       </c>
@@ -7649,7 +8002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>576</v>
       </c>
@@ -7691,7 +8044,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>580</v>
       </c>
@@ -7733,7 +8086,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>584</v>
       </c>
@@ -7775,7 +8128,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>588</v>
       </c>
@@ -7815,7 +8168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>592</v>
       </c>
@@ -7855,7 +8208,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>596</v>
       </c>
@@ -7895,7 +8248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>601</v>
       </c>
@@ -7937,7 +8290,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>605</v>
       </c>
@@ -7977,7 +8330,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>610</v>
       </c>
@@ -8017,7 +8370,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>615</v>
       </c>
@@ -8059,7 +8412,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>619</v>
       </c>
@@ -8101,7 +8454,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>623</v>
       </c>
@@ -8143,7 +8496,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>626</v>
       </c>
@@ -8183,7 +8536,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>630</v>
       </c>
@@ -8223,7 +8576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>633</v>
       </c>
@@ -8265,7 +8618,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>636</v>
       </c>
@@ -8305,7 +8658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>639</v>
       </c>
@@ -8345,7 +8698,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>643</v>
       </c>
@@ -8385,7 +8738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>648</v>
       </c>
@@ -8425,7 +8778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>651</v>
       </c>
@@ -8467,7 +8820,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>655</v>
       </c>
@@ -8509,7 +8862,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>659</v>
       </c>
@@ -8551,7 +8904,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>663</v>
       </c>
@@ -8591,7 +8944,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>667</v>
       </c>
@@ -8633,7 +8986,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>671</v>
       </c>
@@ -8673,7 +9026,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>674</v>
       </c>
@@ -8713,7 +9066,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>677</v>
       </c>
@@ -8753,7 +9106,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>681</v>
       </c>
@@ -8793,7 +9146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>684</v>
       </c>
@@ -8835,7 +9188,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>687</v>
       </c>
@@ -8877,7 +9230,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>691</v>
       </c>
@@ -8917,7 +9270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>695</v>
       </c>
@@ -8957,7 +9310,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>699</v>
       </c>
@@ -8999,7 +9352,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>703</v>
       </c>
@@ -9041,7 +9394,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>707</v>
       </c>
@@ -9081,7 +9434,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>713</v>
       </c>
@@ -9123,7 +9476,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>717</v>
       </c>
@@ -9165,7 +9518,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>721</v>
       </c>
@@ -9207,7 +9560,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>725</v>
       </c>
@@ -9249,7 +9602,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>729</v>
       </c>
@@ -9289,7 +9642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>733</v>
       </c>
@@ -9329,7 +9682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>737</v>
       </c>
@@ -9369,7 +9722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>740</v>
       </c>
@@ -9409,7 +9762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>743</v>
       </c>
@@ -9449,7 +9802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>748</v>
       </c>
@@ -9491,7 +9844,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>751</v>
       </c>
@@ -9531,7 +9884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>755</v>
       </c>
@@ -9573,7 +9926,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>758</v>
       </c>
@@ -9613,7 +9966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>761</v>
       </c>
@@ -9653,7 +10006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>765</v>
       </c>
@@ -9693,7 +10046,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>768</v>
       </c>
@@ -9734,6 +10087,22 @@
       </c>
     </row>
   </sheetData>
-  <headerFooter/>
+  <autoFilter ref="C1:C178" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="23.294.069-7"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 OXXO | Uso Interno</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{08c64559-49c6-47cf-865f-da0233616f0f}" enabled="1" method="Standard" siteId="{66f9ab85-de1a-40d4-b7bb-21565ad57cce}" removed="0"/>
+</clbl:labelList>
 </file>